--- a/output_fixed/validation_report.xlsx
+++ b/output_fixed/validation_report.xlsx
@@ -7,8 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Detailed Comparison" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Detailed Comparison" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,82 +425,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Total Sections in TOC</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Total Sections Parsed</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Sections Matched</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1221</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Sections in TOC only</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Sections in Parsed only</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E1222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
